--- a/stories/arbres/ATOM-SAN.HYG.003-03.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Achille est dans sa chambre. Son nez chatouille. Maman est près du lit. Maman tend un mouchoir. Achille prend le mouchoir. Il se mouche tout doux. Atchoum. Le nez est plus libre. Achille va à la poubelle. Il jette le mouchoir. Maman dit : mouchoir, puis poubelle. Achille se lave les mains. L'eau est tiède. Il essuie ses doigts. Il revient près de maman. Maman sourit. Achille respire mieux. Il s'assoit sur le tapis. Le tapis est doux. Maman dit encore : mouchoir, puis poubelle.</t>
+          <t>Achille est dans sa chambre. Son nez chatouille. Maman est près du lit. Maman tend un mouchoir. Achille prend le mouchoir. Il se mouche tout doux. Atchoum. Le nez est plus libre. Achille va à la poubelle. Il jette le mouchoir. Mouchoir, puis poubelle. Achille se lave les mains. L'eau est tiède. Il essuie ses doigts. Il revient près de maman. Maman sourit. Achille respire mieux. Il s'assoit sur le tapis. Le tapis est doux. Maman dit encore : mouchoir, puis poubelle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Achille est dans sa chambre. Son nez chatouille. Maman est près du lit. Maman tend un mouchoir. Achille prend le mouchoir. Il se mouche tout doux. Atchoum. Le nez est plus libre. Achille va à la poubelle. Il jette le mouchoir.
+maman|Mouchoir, puis poubelle.
+narrateur|Achille se lave les mains. L'eau est tiède. Il essuie ses doigts. Il revient près de maman. Maman sourit. Achille respire mieux. Il s'assoit sur le tapis. Le tapis est doux. Maman dit encore : mouchoir, puis poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Achille se mouche. Que prend-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Achille a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Achille s'assoit près de maman. Son nez est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-03.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Achille se lave les mains. L'eau est tiède. Il essuie ses doigts. Il revient près de maman. Maman sourit. Achille respire mieux. Il s'assoit sur le tapis. Le tapis est doux. Maman dit encore : mouchoir, puis poubelle.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Achille se mouche. Que prend-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Achille a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1837,7 @@
           <t>narrateur|Achille s'assoit près de maman. Son nez est calme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.003-03.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le mouchoir d'Achille</t>
+          <t>Le mouchoir de Victorino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un livre ouvert montre un bateau. Le doudou attend. Le nez de Victorino chatouille. Mouchoir, puis poubelle.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Achille est dans sa chambre. Son nez chatouille. Maman est près du lit. Maman tend un mouchoir. Achille prend le mouchoir. Il se mouche tout doux. Atchoum. Le nez est plus libre. Achille va à la poubelle. Il jette le mouchoir. Mouchoir, puis poubelle. Achille se lave les mains. L'eau est tiède. Il essuie ses doigts. Il revient près de maman. Maman sourit. Achille respire mieux. Il s'assoit sur le tapis. Le tapis est doux. Maman dit encore : mouchoir, puis poubelle.</t>
+          <t>Un livre ouvert montre un bateau bleu. Le doudou ours attend sur l'oreiller. Le rideau rayé bouge un peu. Le tapis est épais sous les genoux. Une veilleuse fait un rond orange. Victorino, tu vois le bateau ? Oui. Il est bleu. Le doudou t'attend. Il est sur l'oreiller. En ce moment, Victorino est dans sa chambre. Il pose la main sur le tapis. Son nez chatouille. Atchoum. Ton nez chatouille ? Oui, maman. Maman est près du lit. Maman tend un mouchoir. Prends un mouchoir. Victorino prend le mouchoir. Le papier est doux. Il se mouche, tout doux. Atchoum. Le nez est plus libre. Je respire. Victorino va à la poubelle. Il jette le mouchoir. Mouchoir, puis poubelle. Dans la poubelle. Bravo. Tu as jeté le mouchoir. C'est du bon travail. Victorino se lave les mains. L'eau est tiède. Il essuie ses doigts. Tu as fini de laver tes mains ? Oui, maman. Il revient près de maman. Il s'assoit sur le tapis. Le tapis est doux. Tu respires mieux ? Oui. Le nez est calme. Mouchoir, puis poubelle. Mouchoir, poubelle. Oui. Bravo, Victorino. Le doudou ours reste sur l'oreiller. Le rond orange est toujours là. On range le livre, après. Après le doudou ? Oui. Tout doux. Victorino touche la page du bateau. Le papier est lisse. Le bateau a une voile. Elle est blanche. Ton nez reste calme ? Oui. Mouchoir, poubelle. Bravo. C'est du bon travail. Le rideau rayé s'arrête. Le tapis sent le linge propre. On ferme le livre, plus tard. Le bateau reste. Oui. Sur la page.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,73 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Achille est dans sa chambre. Son nez chatouille. Maman est près du lit. Maman tend un mouchoir. Achille prend le mouchoir. Il se mouche tout doux. Atchoum. Le nez est plus libre. Achille va à la poubelle. Il jette le mouchoir.
+          <t>narrateur|Un livre ouvert montre un bateau bleu.
+narrateur|Le doudou ours attend sur l'oreiller.
+narrateur|Le rideau rayé bouge un peu.
+narrateur|Le tapis est épais sous les genoux.
+narrateur|Une veilleuse fait un rond orange.
+maman|Victorino, tu vois le bateau ?
+enfant-m|Oui. Il est bleu.
+maman|Le doudou t'attend.
+enfant-m|Il est sur l'oreiller.
+narrateur|En ce moment, Victorino est dans sa chambre.
+narrateur|Il pose la main sur le tapis.
+narrateur|Son nez chatouille.
+enfant-m|Atchoum.
+maman|Ton nez chatouille ?
+enfant-m|Oui, maman.
+narrateur|Maman est près du lit.
+narrateur|Maman tend un mouchoir.
+maman|Prends un mouchoir.
+narrateur|Victorino prend le mouchoir.
+narrateur|Le papier est doux.
+narrateur|Il se mouche, tout doux.
+enfant-m|Atchoum.
+maman|Le nez est plus libre.
+enfant-m|Je respire.
+narrateur|Victorino va à la poubelle.
+narrateur|Il jette le mouchoir.
 maman|Mouchoir, puis poubelle.
-narrateur|Achille se lave les mains. L'eau est tiède. Il essuie ses doigts. Il revient près de maman. Maman sourit. Achille respire mieux. Il s'assoit sur le tapis. Le tapis est doux. Maman dit encore : mouchoir, puis poubelle.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-m|Dans la poubelle.
+maman|Bravo. Tu as jeté le mouchoir.
+maman|C'est du bon travail.
+narrateur|Victorino se lave les mains.
+narrateur|L'eau est tiède.
+narrateur|Il essuie ses doigts.
+maman|Tu as fini de laver tes mains ?
+enfant-m|Oui, maman.
+narrateur|Il revient près de maman.
+narrateur|Il s'assoit sur le tapis.
+narrateur|Le tapis est doux.
+maman|Tu respires mieux ?
+enfant-m|Oui. Le nez est calme.
+maman|Mouchoir, puis poubelle.
+enfant-m|Mouchoir, poubelle.
+maman|Oui. Bravo, Victorino.
+narrateur|Le doudou ours reste sur l'oreiller.
+narrateur|Le rond orange est toujours là.
+maman|On range le livre, après.
+enfant-m|Après le doudou ?
+maman|Oui. Tout doux.
+narrateur|Victorino touche la page du bateau.
+narrateur|Le papier est lisse.
+maman|Le bateau a une voile.
+enfant-m|Elle est blanche.
+maman|Ton nez reste calme ?
+enfant-m|Oui. Mouchoir, poubelle.
+maman|Bravo. C'est du bon travail.
+narrateur|Le rideau rayé s'arrête.
+narrateur|Le tapis sent le linge propre.
+maman|On ferme le livre, plus tard.
+enfant-m|Le bateau reste.
+maman|Oui. Sur la page.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>page_livre</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,7 +1415,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Achille se mouche. Que prend-il ?</t>
+          <t>Victorino se mouche. Que prend-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,10 +1571,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Achille se mouche. Que prend-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Victorino se mouche.
+narrateur|Que prend-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1526,7 +1599,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Achille a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle.</t>
+          <t>Victorino a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle. Tu as pris un mouchoir ? Oui. Puis poubelle. Bravo. C'est du bon travail. Le doudou ours attend encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,10 +1743,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Achille a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorino a pris un mouchoir.
+narrateur|Il s'est mouché.
+narrateur|Il a jeté le mouchoir à la poubelle.
+maman|Tu as pris un mouchoir ?
+enfant-m|Oui. Puis poubelle.
+maman|Bravo. C'est du bon travail.
+narrateur|Le doudou ours attend encore.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1698,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Achille s'assoit près de maman. Son nez est calme.</t>
+          <t>Victorino s'assoit près de maman. Son nez est calme. Tu veux le doudou ? Oui. Contre moi. Maman pose l'ours dans ses bras. Le tapis reste doux. L'oreille de l'ours est pliée. Je la redresse. Tout doux. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1834,10 +1912,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Achille s'assoit près de maman. Son nez est calme.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Victorino s'assoit près de maman.
+narrateur|Son nez est calme.
+maman|Tu veux le doudou ?
+enfant-m|Oui. Contre moi.
+narrateur|Maman pose l'ours dans ses bras.
+narrateur|Le tapis reste doux.
+maman|L'oreille de l'ours est pliée.
+enfant-m|Je la redresse.
+maman|Tout doux. Bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1862,7 +1947,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mouchoir, puis poubelle. Bravo, Victorino. Le bateau bleu reste sur la page. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2002,10 +2087,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|Mouchoir, puis poubelle.
+maman|Bravo, Victorino.
+narrateur|Le bateau bleu reste sur la page.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2149,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-03.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un livre ouvert montre un bateau bleu. Le doudou ours attend sur l'oreiller. Le rideau rayé bouge un peu. Le tapis est épais sous les genoux. Une veilleuse fait un rond orange. Victorino, tu vois le bateau ? Oui. Il est bleu. Le doudou t'attend. Il est sur l'oreiller. En ce moment, Victorino est dans sa chambre. Il pose la main sur le tapis. Son nez chatouille. Atchoum. Ton nez chatouille ? Oui, maman. Maman est près du lit. Maman tend un mouchoir. Prends un mouchoir. Victorino prend le mouchoir. Le papier est doux. Il se mouche, tout doux. Atchoum. Le nez est plus libre. Je respire. Victorino va à la poubelle. Il jette le mouchoir. Mouchoir, puis poubelle. Dans la poubelle. Bravo. Tu as jeté le mouchoir. C'est du bon travail. Victorino se lave les mains. L'eau est tiède. Il essuie ses doigts. Tu as fini de laver tes mains ? Oui, maman. Il revient près de maman. Il s'assoit sur le tapis. Le tapis est doux. Tu respires mieux ? Oui. Le nez est calme. Mouchoir, puis poubelle. Mouchoir, poubelle. Oui. Bravo, Victorino. Le doudou ours reste sur l'oreiller. Le rond orange est toujours là. On range le livre, après. Après le doudou ? Oui. Tout doux. Victorino touche la page du bateau. Le papier est lisse. Le bateau a une voile. Elle est blanche. Ton nez reste calme ? Oui. Mouchoir, poubelle. Bravo. C'est du bon travail. Le rideau rayé s'arrête. Le tapis sent le linge propre. On ferme le livre, plus tard. Le bateau reste. Oui. Sur la page.</t>
+          <t>Un livre ouvert montre un bateau bleu. Le doudou ours attend sur l'oreiller. Le rideau rayé bouge un peu. Le tapis est épais sous les genoux. Une veilleuse fait un rond orange. Victorino, tu vois le bateau ? Oui. Il est bleu. Le doudou t'attend. Il est sur l'oreiller. En ce moment, Victorino est dans sa chambre. Il pose la main sur le tapis. Son nez chatouille. Atchoum. Ton nez chatouille ? Oui, maman. Maman est près du lit. Maman tend un mouchoir. Prends un mouchoir. Victorino prend le mouchoir. Le papier est doux. Il se mouche, tout doux. Atchoum. Le nez est plus libre. Je respire. Victorino va à la poubelle. Il jette le mouchoir. Mouchoir, puis poubelle. Dans la poubelle. Bravo. Tu as jeté le mouchoir. Victorino se lave les mains. L'eau est tiède. Il essuie ses doigts. Tu as fini de laver tes mains ? Oui, maman. Il revient près de maman. Il s'assoit sur le tapis. Le tapis est doux. Tu respires mieux ? Oui. Le nez est calme. Mouchoir, puis poubelle. Mouchoir, poubelle. Oui. Bravo, Victorino. Le doudou ours reste sur l'oreiller. Le rond orange est toujours là. On range le livre, après. Après le doudou ? Oui. Tout doux. Victorino touche la page du bateau. Le papier est lisse. Le bateau a une voile. Elle est blanche. Ton nez reste calme ? Oui. Mouchoir, poubelle. Le rideau rayé s'arrête. Le tapis sent le linge propre. On ferme le livre, plus tard. Le bateau reste. Oui. Sur la page.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Achille est dans sa chambre. Son nez chatouille. Maman est près du lit. Maman tend un &lt;emphasis level="moderate"&gt;mouchoir&lt;/emphasis&gt;. Achille prend le mouchoir. Il se mouche tout doux. Atchoum. Le nez est plus libre. Achille va à la poubelle. Il jette le mouchoir. Maman dit : mouchoir, puis poubelle. Achille se lave les mains. L'eau est tiède. Il essuie ses doigts. Il revient près de maman. Maman sourit. Achille respire mieux. Il s'assoit sur le tapis. Le tapis est doux. Maman dit encore : mouchoir, puis poubelle.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un livre ouvert montre un bateau bleu. Le doudou ours attend sur l'oreiller. Le rideau rayé bouge un peu. Le tapis est épais sous les genoux. Une veilleuse fait un rond orange. Victorino, tu vois le bateau ? Oui. Il est bleu. Le doudou t'attend. Il est sur l'oreiller. En ce moment, Victorino est dans sa chambre. Il pose la main sur le tapis. Son nez chatouille. Atchoum. Ton nez chatouille ? Oui, maman. Maman est près du lit. Maman tend un mouchoir. Prends un mouchoir. Victorino prend le mouchoir. Le papier est doux. Il se mouche, tout doux. Atchoum. Le nez est plus libre. Je respire. Victorino va à la poubelle. Il jette le mouchoir. Mouchoir, puis poubelle. Dans la poubelle. Bravo. Tu as jeté le mouchoir. Victorino se lave les mains. L'eau est tiède. Il essuie ses doigts. Tu as fini de laver tes mains ? Oui, maman. Il revient près de maman. Il s'assoit sur le tapis. Le tapis est doux. Tu respires mieux ? Oui. Le nez est calme. Mouchoir, puis poubelle. Mouchoir, poubelle. Oui. Bravo, Victorino. Le doudou ours reste sur l'oreiller. Le rond orange est toujours là. On range le livre, après. Après le doudou ? Oui. Tout doux. Victorino touche la page du bateau. Le papier est lisse. Le bateau a une voile. Elle est blanche. Ton nez reste calme ? Oui. Mouchoir, poubelle. Le rideau rayé s'arrête. Le tapis sent le linge propre. On ferme le livre, plus tard. Le bateau reste. Oui. Sur la page.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1353,7 +1353,6 @@
 maman|Mouchoir, puis poubelle.
 enfant-m|Dans la poubelle.
 maman|Bravo. Tu as jeté le mouchoir.
-maman|C'est du bon travail.
 narrateur|Victorino se lave les mains.
 narrateur|L'eau est tiède.
 narrateur|Il essuie ses doigts.
@@ -1378,7 +1377,6 @@
 enfant-m|Elle est blanche.
 maman|Ton nez reste calme ?
 enfant-m|Oui. Mouchoir, poubelle.
-maman|Bravo. C'est du bon travail.
 narrateur|Le rideau rayé s'arrête.
 narrateur|Le tapis sent le linge propre.
 maman|On ferme le livre, plus tard.
@@ -1420,7 +1418,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Achille se mouche. Que prend-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino se mouche. Que prend-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1599,12 +1597,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle. Tu as pris un mouchoir ? Oui. Puis poubelle. Bravo. C'est du bon travail. Le doudou ours attend encore.</t>
+          <t>Victorino a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle. Tu as pris un mouchoir ? Oui. Puis poubelle. Le doudou ours attend encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Achille a pris un &lt;emphasis level="moderate"&gt;mouchoir&lt;/emphasis&gt;. Il s'est mouché. Il a jeté le mouchoir à la poubelle.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle. Tu as pris un mouchoir ? Oui. Puis poubelle. Le doudou ours attend encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1748,7 +1746,6 @@
 narrateur|Il a jeté le mouchoir à la poubelle.
 maman|Tu as pris un mouchoir ?
 enfant-m|Oui. Puis poubelle.
-maman|Bravo. C'est du bon travail.
 narrateur|Le doudou ours attend encore.</t>
         </is>
       </c>
@@ -1781,7 +1778,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Achille s'assoit près de maman. Son nez est calme.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino s'assoit près de maman. Son nez est calme. Tu veux le doudou ? Oui. Contre moi. Maman pose l'ours dans ses bras. Le tapis reste doux. L'oreille de l'ours est pliée. Je la redresse. Tout doux. Bravo.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1947,12 +1944,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mouchoir, puis poubelle. Bravo, Victorino. Le bateau bleu reste sur la page. L'histoire est finie.</t>
+          <t>Mouchoir, puis poubelle. Bravo, Victorino. Le bateau bleu reste sur la page.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mouchoir, puis poubelle. Bravo, Victorino. Le bateau bleu reste sur la page.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2089,8 +2086,7 @@
         <is>
           <t>enfant-m|Mouchoir, puis poubelle.
 maman|Bravo, Victorino.
-narrateur|Le bateau bleu reste sur la page.
-narrateur|L'histoire est finie.</t>
+narrateur|Le bateau bleu reste sur la page.</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2156,6 +2152,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-03.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chambre</t>
+          <t>chambre, livre, doudou, tapis épais</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Achille, maman</t>
+          <t>Victorino, maman</t>
         </is>
       </c>
     </row>
